--- a/RuoYi-Vue-springboot3/ruoyi-system/src/main/resources/templates/customs/customs-declaration-template.xlsx
+++ b/RuoYi-Vue-springboot3/ruoyi-system/src/main/resources/templates/customs/customs-declaration-template.xlsx
@@ -2,18 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11595"/>
+    <workbookView windowWidth="22188" windowHeight="10295"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="合同" sheetId="7" r:id="rId1"/>
+    <sheet name="INVOICE" sheetId="9" r:id="rId2"/>
+    <sheet name="Packing List " sheetId="10" r:id="rId3"/>
+    <sheet name="报关单" sheetId="12" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId4"/>
-  </externalReferences>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">报关单!$A$1:$M$14</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">合同!$15:$15</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -32,7 +34,331 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="108">
+  <si>
+    <t>成都玖马赫供应链管理有限公司</t>
+  </si>
+  <si>
+    <t>CHENGDU JUMACH SUPPLY CHAIN MANAGEMENT CO.,LTD</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="22"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>合</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="22"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="22"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>同</t>
+    </r>
+  </si>
+  <si>
+    <t>CONTRACT</t>
+  </si>
+  <si>
+    <t>SELLER</t>
+  </si>
+  <si>
+    <t>PO NUMBER</t>
+  </si>
+  <si>
+    <t>RVG10645-260529-0004</t>
+  </si>
+  <si>
+    <t>CHENGDU JUMACH SUPPLY CHAIN MANAGEMENT CO.,LTD                  1st Floor, Building 12, No. 3 Tianhe Road, Chengdu High-tech Zone,Sichuan,China
+TEL:(0086)19282017790</t>
+  </si>
+  <si>
+    <t>PO DATE</t>
+  </si>
+  <si>
+    <t>SHIP TO</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>PRICE TERM</t>
+  </si>
+  <si>
+    <t>TRANSPORT</t>
+  </si>
+  <si>
+    <t>VIA  SEA</t>
+  </si>
+  <si>
+    <t>DELIVERY</t>
+  </si>
+  <si>
+    <t>SEE BELOW REMARK</t>
+  </si>
+  <si>
+    <t>TOTAL AMOUNT</t>
+  </si>
+  <si>
+    <t>BUYER</t>
+  </si>
+  <si>
+    <t>PAYMENT TERM</t>
+  </si>
+  <si>
+    <t>TT</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Hong Kong Cammy Yeson Limited
+C/O 1175 Florence Columbus Road UNITB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
+      <t>A12-A35</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Bordentown New Jersey 08505</t>
+    </r>
+  </si>
+  <si>
+    <t>LINE</t>
+  </si>
+  <si>
+    <t>DESCRIPTION</t>
+  </si>
+  <si>
+    <t>SKU</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>UNIT</t>
+  </si>
+  <si>
+    <t>QUANTITY</t>
+  </si>
+  <si>
+    <t>UNIT PRICE</t>
+  </si>
+  <si>
+    <t>REMARK</t>
+  </si>
+  <si>
+    <t>WE CONFIRM TO ACCEPT THIS PO AS THE ABOVE TERMS</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">                   </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u val="double"/>
+        <sz val="11"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
+      <t>SELLER</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">             </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <u/>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Signature for and on behalf of the Seller</t>
+    </r>
+  </si>
+  <si>
+    <t>Signature for and on behalf of the Buyer</t>
+  </si>
+  <si>
+    <t>1st Floor, Building 12, No. 3 Tianhe Road, Chengdu High-tech ZoneSichuan,China</t>
+  </si>
+  <si>
+    <t>商 业 发 票</t>
+  </si>
+  <si>
+    <t>COMMERCIAL INVOICE</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>TO</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Hong Kong Cammy Yeson Limited</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>C/O 1175 Florence Columbus Road UNITB</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>A12-A35</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Bordentown New Jersey 08505</t>
+    </r>
+  </si>
+  <si>
+    <t>INV. NO:</t>
+  </si>
+  <si>
+    <t>INV10645-260529-0004</t>
+  </si>
+  <si>
+    <t>DATE:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESCRIPTION </t>
+  </si>
+  <si>
+    <t>装箱单</t>
+  </si>
+  <si>
+    <t>PACKING LIST</t>
+  </si>
+  <si>
+    <t>Marks &amp; Nos</t>
+  </si>
+  <si>
+    <t>Description of Goods</t>
+  </si>
+  <si>
+    <t>Quantity/Unit</t>
+  </si>
+  <si>
+    <t>N.W.(KG)</t>
+  </si>
+  <si>
+    <t>G.W.(KG)</t>
+  </si>
+  <si>
+    <t>MEAS.CBM*L*H*W</t>
+  </si>
   <si>
     <r>
       <rPr>
@@ -119,9 +445,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -270,13 +593,13 @@
     <t>纸箱</t>
   </si>
   <si>
-    <t>件数  68</t>
-  </si>
-  <si>
-    <t>毛重（千克）813.6</t>
-  </si>
-  <si>
-    <t>净重  （千克）772.1</t>
+    <t>件数  51</t>
+  </si>
+  <si>
+    <t>毛重（千克）657.1</t>
+  </si>
+  <si>
+    <t>净重  （千克）631.6</t>
   </si>
   <si>
     <t>成交方式   FOB</t>
@@ -349,7 +672,7 @@
     <t>商品名称</t>
   </si>
   <si>
-    <t>SKU（以下信息必须填写在申报要素备注栏）</t>
+    <t>SKU（这个必须填写在申报要素备注栏）</t>
   </si>
   <si>
     <t>规格型号</t>
@@ -485,22 +808,32 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="9">
+    <numFmt numFmtId="26" formatCode="\$#,##0.00_);[Red]\(\$#,##0.00\)"/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="[$-809]d\ mmmm\ yyyy;@"/>
+    <numFmt numFmtId="177" formatCode="\$#,##0.00;\-\$#,##0.00"/>
+    <numFmt numFmtId="178" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
+    <numFmt numFmtId="179" formatCode="&quot;US$&quot;#,##0.00_);[Red]\(&quot;US$&quot;#,##0.00\)"/>
   </numFmts>
-  <fonts count="28">
-    <font>
-      <sz val="11"/>
+  <fonts count="61">
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -545,6 +878,173 @@
       <sz val="9"/>
       <color indexed="8"/>
       <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="돋움"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="돋움"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Courier New"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Courier New"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <name val="Courier New"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <name val="Courier New"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Courier New"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <u val="double"/>
+      <sz val="11"/>
+      <name val="Courier New"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Courier New"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <u/>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -692,13 +1192,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="18"/>
       <color indexed="8"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -708,6 +1226,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799920651875362"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1021,19 +1545,19 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right style="thin">
         <color auto="1"/>
-      </left>
-      <right/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
+      <left style="thin">
         <color auto="1"/>
-      </right>
+      </left>
+      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -1138,283 +1662,589 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="16">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="17">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="16">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="18">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="19">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="20">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="6" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="6" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="7" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="130">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="21" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="26" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="26" fontId="28" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="17" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="17" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="17" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="26" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1468,7 +2298,13 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="00FF0000"/>
+      <color rgb="00FFFF00"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1530,7 +2366,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>370205</xdr:colOff>
+      <xdr:colOff>123825</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>695325</xdr:rowOff>
     </xdr:to>
@@ -1549,92 +2385,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11734165" y="27940"/>
-          <a:ext cx="751840" cy="667385"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>227965</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>781050</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>866140</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="227965" y="0"/>
-          <a:ext cx="553085" cy="866140"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>304165</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>27940</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>370205</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>695325</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 2"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11734165" y="27940"/>
-          <a:ext cx="751840" cy="667385"/>
+          <a:off x="12785090" y="27940"/>
+          <a:ext cx="683260" cy="667385"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1650,35 +2402,10 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="合同"/>
-      <sheetName val="INVOICE"/>
-      <sheetName val="Packing List "/>
-      <sheetName val="报关单"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="5">
-          <cell r="G5" t="str">
-            <v>RVG10645-260604-0001</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
-    <a:clrScheme name="WPS">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1686,39 +2413,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4874CB"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EE822F"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="F2BA02"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="75BD42"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="30C0B4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="E54C5E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0026E5"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="7E1FAD"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="WPS">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1788,132 +2515,169 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="WPS">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumOff val="17500"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:hueOff val="-2520000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:gradFill>
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="phClr">
-                  <a:hueOff val="-4200000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="phClr"/>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="2700000" scaled="1"/>
-          </a:gradFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:schemeClr val="phClr">
-                <a:alpha val="60000"/>
-              </a:schemeClr>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1924,18 +2688,1025 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:I49"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.8916666666667" customWidth="1"/>
-    <col min="2" max="2" width="39.1083333333333" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="1" max="1" width="7.83333333333333" style="80" customWidth="1"/>
+    <col min="2" max="3" width="15.5" style="80" customWidth="1"/>
+    <col min="4" max="4" width="23.25" style="80" customWidth="1"/>
+    <col min="5" max="5" width="7.08333333333333" style="80" customWidth="1"/>
+    <col min="6" max="6" width="14.8333333333333" style="80" customWidth="1"/>
+    <col min="7" max="7" width="12.8333333333333" style="81" customWidth="1"/>
+    <col min="8" max="8" width="14.5833333333333" style="81" customWidth="1"/>
+    <col min="9" max="9" width="19.0833333333333" style="82" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="80"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="80.15" customHeight="1" spans="1:13">
+    <row r="1" ht="23.15" customHeight="1" spans="1:9">
+      <c r="A1" s="83" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+    </row>
+    <row r="2" ht="21" customHeight="1" spans="1:9">
+      <c r="A2" s="85" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="85"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+    </row>
+    <row r="3" ht="26.15" customHeight="1" spans="1:9">
+      <c r="A3" s="86" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="86"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="86"/>
+    </row>
+    <row r="4" s="73" customFormat="1" ht="21" customHeight="1" spans="1:9">
+      <c r="A4" s="87" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="87"/>
+      <c r="C4" s="87"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
+    </row>
+    <row r="5" s="74" customFormat="1" ht="21" customHeight="1" spans="1:9">
+      <c r="A5" s="88" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="91"/>
+      <c r="F5" s="92" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="93" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="93"/>
+      <c r="I5" s="94"/>
+    </row>
+    <row r="6" s="75" customFormat="1" ht="17.25" customHeight="1" spans="1:9">
+      <c r="A6" s="95" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="91"/>
+      <c r="C6" s="91"/>
+      <c r="D6" s="96"/>
+      <c r="E6" s="91"/>
+      <c r="F6" s="97" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="98">
+        <v>46167</v>
+      </c>
+      <c r="H6" s="98"/>
+      <c r="I6" s="99"/>
+    </row>
+    <row r="7" s="75" customFormat="1" ht="17.25" customHeight="1" spans="1:9">
+      <c r="A7" s="95"/>
+      <c r="B7" s="91"/>
+      <c r="C7" s="91"/>
+      <c r="D7" s="96"/>
+      <c r="E7" s="91"/>
+      <c r="F7" s="97" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="100" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="100"/>
+      <c r="I7" s="99"/>
+    </row>
+    <row r="8" s="75" customFormat="1" ht="17.25" customHeight="1" spans="1:9">
+      <c r="A8" s="95"/>
+      <c r="B8" s="91"/>
+      <c r="C8" s="91"/>
+      <c r="D8" s="96"/>
+      <c r="E8" s="91"/>
+      <c r="F8" s="97" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="101"/>
+      <c r="H8" s="101"/>
+      <c r="I8" s="99"/>
+    </row>
+    <row r="9" s="75" customFormat="1" ht="17.25" customHeight="1" spans="1:9">
+      <c r="A9" s="95"/>
+      <c r="B9" s="91"/>
+      <c r="C9" s="91"/>
+      <c r="D9" s="96"/>
+      <c r="E9" s="91"/>
+      <c r="F9" s="102" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="98" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="98"/>
+      <c r="I9" s="99"/>
+    </row>
+    <row r="10" s="75" customFormat="1" ht="17.25" customHeight="1" spans="1:9">
+      <c r="A10" s="95"/>
+      <c r="B10" s="91"/>
+      <c r="C10" s="91"/>
+      <c r="D10" s="96"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="102" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="98" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="103"/>
+      <c r="I10" s="99"/>
+    </row>
+    <row r="11" s="75" customFormat="1" ht="17.25" customHeight="1" spans="1:9">
+      <c r="A11" s="104"/>
+      <c r="B11" s="105"/>
+      <c r="C11" s="105"/>
+      <c r="D11" s="106"/>
+      <c r="E11" s="91"/>
+      <c r="F11" s="97" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="107" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H11" s="107"/>
+      <c r="I11" s="99"/>
+    </row>
+    <row r="12" s="75" customFormat="1" ht="20.25" customHeight="1" spans="1:9">
+      <c r="A12" s="88" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="89"/>
+      <c r="C12" s="89"/>
+      <c r="D12" s="90"/>
+      <c r="E12" s="91"/>
+      <c r="F12" s="97" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="91" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="91"/>
+      <c r="I12" s="96"/>
+    </row>
+    <row r="13" s="75" customFormat="1" ht="15.75" customHeight="1" spans="1:9">
+      <c r="A13" s="95" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="91"/>
+      <c r="C13" s="91"/>
+      <c r="D13" s="96"/>
+      <c r="E13" s="91"/>
+      <c r="F13" s="108"/>
+      <c r="G13" s="91"/>
+      <c r="H13" s="91"/>
+      <c r="I13" s="96"/>
+    </row>
+    <row r="14" s="75" customFormat="1" ht="27" customHeight="1" spans="1:9">
+      <c r="A14" s="104"/>
+      <c r="B14" s="105"/>
+      <c r="C14" s="105"/>
+      <c r="D14" s="106"/>
+      <c r="E14" s="91"/>
+      <c r="F14" s="109"/>
+      <c r="G14" s="105" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="105"/>
+      <c r="I14" s="106"/>
+    </row>
+    <row r="15" s="76" customFormat="1" ht="25" customHeight="1" spans="1:9">
+      <c r="A15" s="110" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="111" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="111" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="111" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="111" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="112" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" s="112" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="113" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" s="76" customFormat="1" ht="25" customHeight="1" spans="1:9">
+      <c r="A16" s="114"/>
+      <c r="B16" s="111"/>
+      <c r="C16" s="111"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="114"/>
+      <c r="F16" s="111"/>
+      <c r="G16" s="115"/>
+      <c r="H16" s="112"/>
+      <c r="I16" s="115"/>
+    </row>
+    <row r="17" s="77" customFormat="1" ht="34" customHeight="1" spans="1:9">
+      <c r="A17" s="116"/>
+      <c r="B17" s="117" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="117"/>
+      <c r="D17" s="117"/>
+      <c r="E17" s="116"/>
+      <c r="F17" s="117"/>
+      <c r="G17" s="118"/>
+      <c r="H17" s="117"/>
+      <c r="I17" s="116"/>
+    </row>
+    <row r="18" s="77" customFormat="1" ht="34" customHeight="1" spans="1:9">
+      <c r="A18" s="116"/>
+      <c r="B18" s="119" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="119"/>
+      <c r="D18" s="119"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="120"/>
+      <c r="G18" s="121"/>
+      <c r="H18" s="120" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" s="116"/>
+    </row>
+    <row r="19" s="77" customFormat="1" ht="34" customHeight="1" spans="1:9">
+      <c r="A19" s="116"/>
+      <c r="B19" s="79"/>
+      <c r="C19" s="79"/>
+      <c r="D19" s="79"/>
+      <c r="E19" s="79"/>
+      <c r="F19" s="79"/>
+      <c r="G19" s="122"/>
+      <c r="H19" s="123"/>
+      <c r="I19" s="123"/>
+    </row>
+    <row r="20" s="77" customFormat="1" ht="34" customHeight="1" spans="1:9">
+      <c r="A20" s="124"/>
+      <c r="B20" s="125" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="125"/>
+      <c r="D20" s="125"/>
+      <c r="E20" s="125"/>
+      <c r="F20" s="126"/>
+      <c r="G20" s="124"/>
+      <c r="H20" s="127" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="127"/>
+    </row>
+    <row r="21" s="77" customFormat="1" ht="34" customHeight="1" spans="1:9">
+      <c r="A21" s="80"/>
+      <c r="B21" s="81"/>
+      <c r="C21" s="81"/>
+      <c r="D21" s="81"/>
+      <c r="E21" s="82"/>
+      <c r="H21" s="128"/>
+    </row>
+    <row r="22" s="77" customFormat="1" ht="34" customHeight="1" spans="1:9">
+      <c r="A22" s="80"/>
+      <c r="B22" s="81"/>
+      <c r="C22" s="81"/>
+      <c r="D22" s="81"/>
+      <c r="E22" s="82"/>
+      <c r="H22" s="128"/>
+    </row>
+    <row r="23" s="77" customFormat="1" ht="34" customHeight="1" spans="1:9">
+      <c r="A23" s="80"/>
+      <c r="B23" s="81"/>
+      <c r="C23" s="81"/>
+      <c r="D23" s="81"/>
+      <c r="E23" s="82"/>
+      <c r="F23" s="129"/>
+      <c r="H23" s="128"/>
+    </row>
+    <row r="24" s="77" customFormat="1" ht="34" customHeight="1" spans="1:9">
+      <c r="A24" s="80"/>
+      <c r="B24" s="81"/>
+      <c r="C24" s="81"/>
+      <c r="D24" s="81"/>
+      <c r="E24" s="82"/>
+      <c r="F24" s="129"/>
+      <c r="H24" s="128"/>
+    </row>
+    <row r="25" s="77" customFormat="1" ht="34" customHeight="1" spans="1:9">
+      <c r="A25" s="80"/>
+      <c r="B25" s="81"/>
+      <c r="C25" s="81"/>
+      <c r="D25" s="81"/>
+      <c r="E25" s="82"/>
+      <c r="H25" s="128"/>
+    </row>
+    <row r="26" s="77" customFormat="1" ht="34" customHeight="1" spans="1:9">
+      <c r="A26" s="80"/>
+      <c r="B26" s="81"/>
+      <c r="C26" s="81"/>
+      <c r="D26" s="81"/>
+      <c r="E26" s="82"/>
+      <c r="H26" s="128"/>
+    </row>
+    <row r="27" s="77" customFormat="1" ht="34" customHeight="1" spans="1:9">
+      <c r="A27" s="80"/>
+      <c r="B27" s="81"/>
+      <c r="C27" s="81"/>
+      <c r="D27" s="81"/>
+      <c r="E27" s="82"/>
+      <c r="F27" s="129"/>
+      <c r="H27" s="128"/>
+    </row>
+    <row r="28" s="78" customFormat="1" ht="24.75" customHeight="1" spans="1:9">
+      <c r="A28" s="80"/>
+      <c r="B28" s="81"/>
+      <c r="C28" s="81"/>
+      <c r="D28" s="81"/>
+      <c r="E28" s="82"/>
+    </row>
+    <row r="29" ht="30.4" customHeight="1" spans="1:9">
+      <c r="B29" s="81"/>
+      <c r="C29" s="81"/>
+      <c r="D29" s="81"/>
+      <c r="E29" s="82"/>
+      <c r="G29" s="80"/>
+      <c r="H29" s="80"/>
+      <c r="I29" s="80"/>
+    </row>
+    <row r="30" s="79" customFormat="1" ht="18" customHeight="1" spans="1:9">
+      <c r="A30" s="80"/>
+      <c r="B30" s="81"/>
+      <c r="C30" s="81"/>
+      <c r="D30" s="81"/>
+      <c r="E30" s="82"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="B31" s="81"/>
+      <c r="C31" s="81"/>
+      <c r="D31" s="81"/>
+      <c r="E31" s="82"/>
+      <c r="G31" s="80"/>
+      <c r="H31" s="80"/>
+      <c r="I31" s="80"/>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="B32" s="81"/>
+      <c r="C32" s="81"/>
+      <c r="D32" s="81"/>
+      <c r="E32" s="82"/>
+      <c r="G32" s="80"/>
+      <c r="H32" s="80"/>
+      <c r="I32" s="80"/>
+    </row>
+    <row r="33" spans="2:9">
+      <c r="B33" s="81"/>
+      <c r="C33" s="81"/>
+      <c r="D33" s="81"/>
+      <c r="E33" s="82"/>
+      <c r="G33" s="80"/>
+      <c r="H33" s="80"/>
+      <c r="I33" s="80"/>
+    </row>
+    <row r="34" spans="2:9">
+      <c r="B34" s="81"/>
+      <c r="C34" s="81"/>
+      <c r="D34" s="81"/>
+      <c r="E34" s="82"/>
+      <c r="G34" s="80"/>
+      <c r="H34" s="80"/>
+      <c r="I34" s="80"/>
+    </row>
+    <row r="35" spans="2:9">
+      <c r="B35" s="81"/>
+      <c r="C35" s="81"/>
+      <c r="D35" s="81"/>
+      <c r="E35" s="82"/>
+      <c r="G35" s="80"/>
+      <c r="H35" s="80"/>
+      <c r="I35" s="80"/>
+    </row>
+    <row r="36" spans="2:9">
+      <c r="B36" s="81"/>
+      <c r="C36" s="81"/>
+      <c r="D36" s="81"/>
+      <c r="E36" s="82"/>
+      <c r="G36" s="80"/>
+      <c r="H36" s="80"/>
+      <c r="I36" s="80"/>
+    </row>
+    <row r="37" spans="2:9">
+      <c r="B37" s="81"/>
+      <c r="C37" s="81"/>
+      <c r="D37" s="81"/>
+      <c r="E37" s="82"/>
+      <c r="G37" s="80"/>
+      <c r="H37" s="80"/>
+      <c r="I37" s="80"/>
+    </row>
+    <row r="38" spans="2:9">
+      <c r="B38" s="81"/>
+      <c r="C38" s="81"/>
+      <c r="D38" s="81"/>
+      <c r="E38" s="82"/>
+      <c r="G38" s="80"/>
+      <c r="H38" s="80"/>
+      <c r="I38" s="80"/>
+    </row>
+    <row r="39" spans="2:9">
+      <c r="B39" s="81"/>
+      <c r="C39" s="81"/>
+      <c r="D39" s="81"/>
+      <c r="E39" s="82"/>
+      <c r="G39" s="80"/>
+      <c r="H39" s="80"/>
+      <c r="I39" s="80"/>
+    </row>
+    <row r="40" spans="2:9">
+      <c r="B40" s="81"/>
+      <c r="C40" s="81"/>
+      <c r="D40" s="81"/>
+      <c r="E40" s="82"/>
+      <c r="G40" s="80"/>
+      <c r="H40" s="80"/>
+      <c r="I40" s="80"/>
+    </row>
+    <row r="41" spans="2:9">
+      <c r="B41" s="81"/>
+      <c r="C41" s="81"/>
+      <c r="D41" s="81"/>
+      <c r="E41" s="82"/>
+      <c r="G41" s="80"/>
+      <c r="H41" s="80"/>
+      <c r="I41" s="80"/>
+    </row>
+    <row r="42" spans="2:9">
+      <c r="B42" s="81"/>
+      <c r="C42" s="81"/>
+      <c r="D42" s="81"/>
+      <c r="E42" s="82"/>
+      <c r="G42" s="80"/>
+      <c r="H42" s="80"/>
+      <c r="I42" s="80"/>
+    </row>
+    <row r="43" spans="2:9">
+      <c r="B43" s="81"/>
+      <c r="C43" s="81"/>
+      <c r="D43" s="81"/>
+      <c r="E43" s="82"/>
+      <c r="G43" s="80"/>
+      <c r="H43" s="80"/>
+      <c r="I43" s="80"/>
+    </row>
+    <row r="44" spans="2:9">
+      <c r="B44" s="81"/>
+      <c r="C44" s="81"/>
+      <c r="D44" s="81"/>
+      <c r="E44" s="82"/>
+      <c r="G44" s="80"/>
+      <c r="H44" s="80"/>
+      <c r="I44" s="80"/>
+    </row>
+    <row r="45" spans="2:9">
+      <c r="B45" s="81"/>
+      <c r="C45" s="81"/>
+      <c r="D45" s="81"/>
+      <c r="E45" s="82"/>
+      <c r="G45" s="80"/>
+      <c r="H45" s="80"/>
+      <c r="I45" s="80"/>
+    </row>
+    <row r="46" spans="2:9">
+      <c r="B46" s="81"/>
+      <c r="C46" s="81"/>
+      <c r="D46" s="81"/>
+      <c r="E46" s="82"/>
+      <c r="G46" s="80"/>
+      <c r="H46" s="80"/>
+      <c r="I46" s="80"/>
+    </row>
+    <row r="47" spans="2:9">
+      <c r="B47" s="81"/>
+      <c r="C47" s="81"/>
+      <c r="D47" s="81"/>
+      <c r="E47" s="82"/>
+      <c r="G47" s="80"/>
+      <c r="H47" s="80"/>
+      <c r="I47" s="80"/>
+    </row>
+    <row r="48" spans="2:9">
+      <c r="B48" s="81"/>
+      <c r="C48" s="81"/>
+      <c r="D48" s="81"/>
+      <c r="E48" s="82"/>
+      <c r="G48" s="80"/>
+      <c r="H48" s="80"/>
+      <c r="I48" s="80"/>
+    </row>
+    <row r="49" spans="2:9">
+      <c r="B49" s="81"/>
+      <c r="C49" s="81"/>
+      <c r="D49" s="81"/>
+      <c r="E49" s="82"/>
+      <c r="G49" s="80"/>
+      <c r="H49" s="80"/>
+      <c r="I49" s="80"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" formatCells="0"/>
+  <mergeCells count="13">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="A6:D11"/>
+    <mergeCell ref="A13:D14"/>
+    <mergeCell ref="G12:I13"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.0784722222222222" right="0.0784722222222222" top="1.10208333333333" bottom="1.25972222222222" header="0.472222222222222" footer="0.550694444444444"/>
+  <pageSetup paperSize="9" scale="77" orientation="portrait"/>
+  <headerFooter scaleWithDoc="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="15.6" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="6.08333333333333" style="49" customWidth="1"/>
+    <col min="2" max="3" width="25.3333333333333" style="49" customWidth="1"/>
+    <col min="4" max="4" width="11.0833333333333" style="49" customWidth="1"/>
+    <col min="5" max="5" width="9.08333333333333" style="49" customWidth="1"/>
+    <col min="6" max="6" width="7.25" style="49" customWidth="1"/>
+    <col min="7" max="7" width="10.0833333333333" style="49" customWidth="1"/>
+    <col min="8" max="8" width="13.25" style="49" customWidth="1"/>
+    <col min="9" max="16364" width="8" style="50"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="35.15" customHeight="1" spans="1:8">
+      <c r="A1" s="51" t="str">
+        <f>合同!A1</f>
+        <v>成都玖马赫供应链管理有限公司</v>
+      </c>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+    </row>
+    <row r="2" ht="26.15" customHeight="1" spans="1:8">
+      <c r="A2" s="67" t="str">
+        <f>合同!A2</f>
+        <v>CHENGDU JUMACH SUPPLY CHAIN MANAGEMENT CO.,LTD</v>
+      </c>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:8">
+      <c r="A3" s="68" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+    </row>
+    <row r="4" ht="20.4" spans="1:8">
+      <c r="A4" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+    </row>
+    <row r="5" s="48" customFormat="1" ht="21" spans="1:8">
+      <c r="A5" s="54" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+    </row>
+    <row r="6" s="48" customFormat="1" ht="21" spans="1:8">
+      <c r="A6" s="69" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="69"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
+    </row>
+    <row r="7" s="48" customFormat="1" ht="28" customHeight="1" spans="1:8">
+      <c r="A7" s="71" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="71"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="59" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="70" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="70"/>
+    </row>
+    <row r="8" s="48" customFormat="1" ht="24" customHeight="1" spans="1:8">
+      <c r="A8" s="71"/>
+      <c r="B8" s="71"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="60"/>
+    </row>
+    <row r="9" s="48" customFormat="1" ht="21" spans="1:8">
+      <c r="A9" s="72" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="61">
+        <f>合同!G6</f>
+        <v>46167</v>
+      </c>
+      <c r="H9" s="61"/>
+    </row>
+    <row r="10" s="49" customFormat="1" ht="34" customHeight="1" spans="1:8">
+      <c r="A10" s="62" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="63" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="63" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="63" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="63" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sort="0" autoFilter="0" pivotTables="0"/>
+  <mergeCells count="10">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="A7:B8"/>
+  </mergeCells>
+  <pageMargins left="0.39" right="0.39" top="0.39" bottom="0.39" header="0.39" footer="0.39"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="6.33333333333333" style="49" customWidth="1"/>
+    <col min="2" max="2" width="25.0833333333333" style="49" customWidth="1"/>
+    <col min="3" max="3" width="20.25" style="49" customWidth="1"/>
+    <col min="4" max="4" width="10.25" style="49" customWidth="1"/>
+    <col min="5" max="5" width="6.08333333333333" style="49" customWidth="1"/>
+    <col min="6" max="6" width="6" style="49" customWidth="1"/>
+    <col min="7" max="7" width="6.75" style="49" customWidth="1"/>
+    <col min="8" max="8" width="7.75" style="49" customWidth="1"/>
+    <col min="9" max="9" width="6.08333333333333" style="49" customWidth="1"/>
+    <col min="10" max="12" width="3.75" style="49" customWidth="1"/>
+    <col min="13" max="13" width="8.33333333333333" style="50"/>
+    <col min="14" max="16384" width="8" style="50"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1" spans="1:13">
+      <c r="A1" s="51" t="str">
+        <f>合同!A1</f>
+        <v>成都玖马赫供应链管理有限公司</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+    </row>
+    <row r="2" ht="27" customHeight="1" spans="1:13">
+      <c r="A2" s="51" t="str">
+        <f>合同!A2</f>
+        <v>CHENGDU JUMACH SUPPLY CHAIN MANAGEMENT CO.,LTD</v>
+      </c>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:13">
+      <c r="A3" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="52"/>
+    </row>
+    <row r="4" ht="20.4" spans="1:13">
+      <c r="A4" s="53" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="53"/>
+    </row>
+    <row r="5" s="48" customFormat="1" ht="21" spans="1:13">
+      <c r="A5" s="54" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
+    </row>
+    <row r="6" s="48" customFormat="1" ht="21" spans="1:13">
+      <c r="A6" s="55" t="str">
+        <f>INVOICE!A6</f>
+        <v>TO：Hong Kong Cammy Yeson Limited</v>
+      </c>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="54"/>
+    </row>
+    <row r="7" s="48" customFormat="1" ht="30" customHeight="1" spans="1:13">
+      <c r="A7" s="58" t="str">
+        <f>INVOICE!A7</f>
+        <v>C/O 1175 Florence Columbus Road UNITB（A12-A35）Bordentown New Jersey 08505</v>
+      </c>
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="59" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="60" t="str">
+        <f>INVOICE!G7</f>
+        <v>INV10645-260529-0004</v>
+      </c>
+      <c r="I7" s="60"/>
+      <c r="J7" s="60"/>
+      <c r="K7" s="60"/>
+      <c r="L7" s="60"/>
+    </row>
+    <row r="8" s="48" customFormat="1" ht="30" customHeight="1" spans="1:13">
+      <c r="A8" s="58"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="61">
+        <f>INVOICE!G9</f>
+        <v>46167</v>
+      </c>
+      <c r="I8" s="61"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="61"/>
+    </row>
+    <row r="9" s="49" customFormat="1" ht="38.15" customHeight="1" spans="1:13">
+      <c r="A9" s="62" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="62" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="62" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="62" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="63" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="62" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="62" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="65" t="s">
+        <v>49</v>
+      </c>
+      <c r="J9" s="65"/>
+      <c r="K9" s="65"/>
+      <c r="L9" s="65"/>
+    </row>
+    <row r="10" s="49" customFormat="1" ht="35.25" customHeight="1" spans="1:13">
+      <c r="M10" s="66"/>
+    </row>
+    <row r="11" s="49" customFormat="1" ht="35.25" customHeight="1"/>
+    <row r="12" s="49" customFormat="1" ht="35.25" customHeight="1"/>
+    <row r="13" s="49" customFormat="1" ht="35.25" customHeight="1"/>
+    <row r="14" s="49" customFormat="1" ht="35.25" customHeight="1"/>
+    <row r="15" s="49" customFormat="1" ht="35.25" customHeight="1"/>
+    <row r="16" s="49" customFormat="1" ht="35.25" customHeight="1"/>
+    <row r="17" s="49" customFormat="1" ht="35.25" customHeight="1"/>
+    <row r="18" s="49" customFormat="1" ht="25" customHeight="1"/>
+    <row r="19" s="49" customFormat="1" ht="27" customHeight="1"/>
+    <row r="20" s="49" customFormat="1" ht="34.5" customHeight="1"/>
+    <row r="21" s="49" customFormat="1" ht="27" customHeight="1"/>
+  </sheetData>
+  <sheetProtection sort="0" autoFilter="0" pivotTables="0"/>
+  <mergeCells count="9">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="H7:L7"/>
+    <mergeCell ref="H8:L8"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="A7:B8"/>
+  </mergeCells>
+  <pageMargins left="0.550694444444444" right="0.393055555555556" top="0.236111111111111" bottom="0" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="A1:M15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="14.0833333333333" style="3" customWidth="1"/>
+    <col min="2" max="2" width="26.25" style="3" customWidth="1"/>
+    <col min="3" max="3" width="13.5833333333333" style="3" customWidth="1"/>
+    <col min="4" max="4" width="25.625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="20.25" style="3" customWidth="1"/>
+    <col min="6" max="6" width="16" style="3" customWidth="1"/>
+    <col min="7" max="7" width="18.5" style="3" customWidth="1"/>
+    <col min="8" max="8" width="8.58333333333333" style="3" customWidth="1"/>
+    <col min="9" max="9" width="7" style="3" customWidth="1"/>
+    <col min="10" max="10" width="7.08333333333333" style="3" customWidth="1"/>
+    <col min="11" max="11" width="6.83333333333333" style="3" customWidth="1"/>
+    <col min="12" max="12" width="11.3333333333333" style="3" customWidth="1"/>
+    <col min="13" max="13" width="9.83333333333333" style="3" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="80.15" customHeight="1" spans="1:13">
       <c r="B1" s="4" t="s">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -1949,13 +3720,13 @@
       <c r="L1" s="4"/>
       <c r="M1" s="5"/>
     </row>
-    <row r="2" s="2" customFormat="1" ht="24.75" customHeight="1" spans="1:13">
+    <row r="2" s="1" customFormat="1" ht="24.75" customHeight="1" spans="1:13">
       <c r="A2" s="6" t="s">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6" t="s">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="8"/>
@@ -1967,56 +3738,56 @@
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
       <c r="M2" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" s="2" customFormat="1" ht="24.75" customHeight="1" spans="1:13">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="24.75" customHeight="1" spans="1:13">
       <c r="A3" s="10" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="8"/>
       <c r="F3" s="10" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="10" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J3" s="13"/>
       <c r="K3" s="10" t="s">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
     </row>
-    <row r="4" s="2" customFormat="1" ht="18" customHeight="1" spans="1:13">
+    <row r="4" s="1" customFormat="1" ht="18" customHeight="1" spans="1:13">
       <c r="A4" s="14" t="s">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="D4" s="7"/>
       <c r="E4" s="8"/>
       <c r="F4" s="10" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="10" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="I4" s="10"/>
       <c r="J4" s="10"/>
@@ -2024,30 +3795,30 @@
       <c r="L4" s="10"/>
       <c r="M4" s="10"/>
     </row>
-    <row r="5" s="2" customFormat="1" ht="24.75" customHeight="1" spans="1:13">
+    <row r="5" s="1" customFormat="1" ht="24.75" customHeight="1" spans="1:13">
       <c r="A5" s="10" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="I5" s="10"/>
       <c r="J5" s="10"/>
@@ -2055,81 +3826,81 @@
       <c r="L5" s="10"/>
       <c r="M5" s="10"/>
     </row>
-    <row r="6" s="2" customFormat="1" ht="24.75" customHeight="1" spans="1:13">
+    <row r="6" s="1" customFormat="1" ht="24.75" customHeight="1" spans="1:13">
       <c r="A6" s="10" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="B6" s="11" t="str">
-        <f>[1]合同!G5</f>
-        <v>RVG10645-260604-0001</v>
+        <f>合同!G5</f>
+        <v>RVG10645-260529-0004</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="10" t="s">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J6" s="13"/>
       <c r="K6" s="10" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M6" s="13"/>
     </row>
-    <row r="7" s="2" customFormat="1" ht="24.75" customHeight="1" spans="1:13">
+    <row r="7" s="1" customFormat="1" ht="24.75" customHeight="1" spans="1:13">
       <c r="A7" s="10" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="16" t="s">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="I7" s="10"/>
       <c r="J7" s="10" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="K7" s="10"/>
       <c r="L7" s="10" t="s">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="M7" s="10"/>
     </row>
-    <row r="8" s="2" customFormat="1" ht="24.75" customHeight="1" spans="1:13">
+    <row r="8" s="1" customFormat="1" ht="24.75" customHeight="1" spans="1:13">
       <c r="A8" s="18" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="19"/>
@@ -2143,9 +3914,9 @@
       <c r="L8" s="19"/>
       <c r="M8" s="20"/>
     </row>
-    <row r="9" s="2" customFormat="1" ht="30" customHeight="1" spans="1:13">
+    <row r="9" s="1" customFormat="1" ht="30" customHeight="1" spans="1:13">
       <c r="A9" s="21" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="B9" s="22"/>
       <c r="C9" s="22"/>
@@ -2160,104 +3931,108 @@
       <c r="L9" s="22"/>
       <c r="M9" s="23"/>
     </row>
-    <row r="10" s="3" customFormat="1" ht="45" spans="1:13">
+    <row r="10" s="2" customFormat="1" ht="21.6" spans="1:13">
       <c r="A10" s="24" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="H10" s="29" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="I10" s="25" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="J10" s="25"/>
       <c r="K10" s="25" t="s">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="L10" s="25"/>
       <c r="M10" s="30" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="25" t="s">
-        <v>54</v>
-      </c>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" spans="1:13">
+      <c r="B11" s="25"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="32"/>
       <c r="F11" s="25"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="34"/>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="35"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="33"/>
-      <c r="M12" s="34"/>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="G13" s="23"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="41"/>
-      <c r="K13" s="41"/>
-      <c r="L13" s="41"/>
-      <c r="M13" s="42"/>
-    </row>
+      <c r="G11" s="33"/>
+      <c r="H11" s="34"/>
+      <c r="M11" s="35"/>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="11.4" spans="1:13">
+      <c r="A12" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="F12" s="25"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="L12" s="38"/>
+      <c r="M12" s="39"/>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="10.8" spans="1:13">
+      <c r="A13" s="40"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="37"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="L13" s="38"/>
+      <c r="M13" s="39"/>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="11.4" spans="1:13">
+      <c r="A14" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="G14" s="23"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="47"/>
+    </row>
+    <row r="15" s="1" customFormat="1"/>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B1:L1"/>
@@ -2277,37 +4052,13 @@
     <mergeCell ref="B9:M9"/>
     <mergeCell ref="I10:J10"/>
     <mergeCell ref="K10:L10"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H11:M13"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H12:M14"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.156944444444444" right="0.156944444444444" top="0.236111111111111" bottom="0.156944444444444" header="0.310416666666667" footer="0.310416666666667"/>
+  <pageSetup paperSize="9" scale="25" orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/RuoYi-Vue-springboot3/ruoyi-system/src/main/resources/templates/customs/customs-declaration-template.xlsx
+++ b/RuoYi-Vue-springboot3/ruoyi-system/src/main/resources/templates/customs/customs-declaration-template.xlsx
@@ -736,10 +736,10 @@
     </r>
   </si>
   <si>
-    <t>原产国（地区</t>
-  </si>
-  <si>
-    <t>最终目的国（地区</t>
+    <t>原产国（地区）</t>
+  </si>
+  <si>
+    <t>最终目的国（地区）</t>
   </si>
   <si>
     <r>
@@ -1518,6 +1518,15 @@
         <color auto="1"/>
       </left>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -1549,15 +1558,6 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -1808,7 +1808,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1879,76 +1879,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2059,7 +2009,7 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -2079,11 +2029,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -2091,39 +2037,43 @@
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="20" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="178" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="177" fontId="21" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="21" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -2135,7 +2085,7 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="26" fontId="28" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="26" fontId="28" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2159,7 +2109,7 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -2167,75 +2117,91 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="179" fontId="17" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="179" fontId="17" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="179" fontId="17" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="179" fontId="17" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="17" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="26" fontId="29" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="26" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -2692,566 +2658,569 @@
   <dimension ref="A1:I49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.83333333333333" style="80" customWidth="1"/>
-    <col min="2" max="3" width="15.5" style="80" customWidth="1"/>
-    <col min="4" max="4" width="23.25" style="80" customWidth="1"/>
-    <col min="5" max="5" width="7.08333333333333" style="80" customWidth="1"/>
-    <col min="6" max="6" width="14.8333333333333" style="80" customWidth="1"/>
-    <col min="7" max="7" width="12.8333333333333" style="81" customWidth="1"/>
-    <col min="8" max="8" width="14.5833333333333" style="81" customWidth="1"/>
-    <col min="9" max="9" width="19.0833333333333" style="82" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="80"/>
+    <col min="1" max="1" width="7.83333333333333" style="64" customWidth="1"/>
+    <col min="2" max="3" width="15.5" style="64" customWidth="1"/>
+    <col min="4" max="4" width="23.25" style="64" customWidth="1"/>
+    <col min="5" max="5" width="7.08333333333333" style="64" customWidth="1"/>
+    <col min="6" max="6" width="14.8333333333333" style="64" customWidth="1"/>
+    <col min="7" max="7" width="12.8333333333333" style="65" customWidth="1"/>
+    <col min="8" max="8" width="14.5833333333333" style="65" customWidth="1"/>
+    <col min="9" max="9" width="19.0833333333333" style="66" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="64"/>
   </cols>
   <sheetData>
     <row r="1" ht="23.15" customHeight="1" spans="1:9">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:9">
-      <c r="A2" s="85" t="s">
+      <c r="A2" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
     </row>
     <row r="3" ht="26.15" customHeight="1" spans="1:9">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="86"/>
-      <c r="C3" s="86"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86"/>
-    </row>
-    <row r="4" s="73" customFormat="1" ht="21" customHeight="1" spans="1:9">
-      <c r="A4" s="87" t="s">
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
+      <c r="I3" s="70"/>
+    </row>
+    <row r="4" s="57" customFormat="1" ht="21" customHeight="1" spans="1:9">
+      <c r="A4" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="87"/>
-      <c r="C4" s="87"/>
-      <c r="D4" s="87"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="87"/>
-      <c r="H4" s="87"/>
-      <c r="I4" s="87"/>
-    </row>
-    <row r="5" s="74" customFormat="1" ht="21" customHeight="1" spans="1:9">
-      <c r="A5" s="88" t="s">
+      <c r="B4" s="71"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+    </row>
+    <row r="5" s="58" customFormat="1" ht="21" customHeight="1" spans="1:9">
+      <c r="A5" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="90"/>
-      <c r="E5" s="91"/>
-      <c r="F5" s="92" t="s">
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="93" t="s">
+      <c r="G5" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="93"/>
-      <c r="I5" s="94"/>
-    </row>
-    <row r="6" s="75" customFormat="1" ht="17.25" customHeight="1" spans="1:9">
-      <c r="A6" s="95" t="s">
+      <c r="H5" s="77"/>
+      <c r="I5" s="78"/>
+    </row>
+    <row r="6" s="59" customFormat="1" ht="17.25" customHeight="1" spans="1:9">
+      <c r="A6" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="91"/>
-      <c r="C6" s="91"/>
-      <c r="D6" s="96"/>
-      <c r="E6" s="91"/>
-      <c r="F6" s="97" t="s">
+      <c r="B6" s="75"/>
+      <c r="C6" s="75"/>
+      <c r="D6" s="80"/>
+      <c r="E6" s="75"/>
+      <c r="F6" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="98">
+      <c r="G6" s="82">
         <v>46167</v>
       </c>
-      <c r="H6" s="98"/>
-      <c r="I6" s="99"/>
-    </row>
-    <row r="7" s="75" customFormat="1" ht="17.25" customHeight="1" spans="1:9">
-      <c r="A7" s="95"/>
-      <c r="B7" s="91"/>
-      <c r="C7" s="91"/>
-      <c r="D7" s="96"/>
-      <c r="E7" s="91"/>
-      <c r="F7" s="97" t="s">
+      <c r="H6" s="82"/>
+      <c r="I6" s="83"/>
+    </row>
+    <row r="7" s="59" customFormat="1" ht="17.25" customHeight="1" spans="1:9">
+      <c r="A7" s="79"/>
+      <c r="B7" s="75"/>
+      <c r="C7" s="75"/>
+      <c r="D7" s="80"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="100" t="s">
+      <c r="G7" s="84" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="100"/>
-      <c r="I7" s="99"/>
-    </row>
-    <row r="8" s="75" customFormat="1" ht="17.25" customHeight="1" spans="1:9">
-      <c r="A8" s="95"/>
-      <c r="B8" s="91"/>
-      <c r="C8" s="91"/>
-      <c r="D8" s="96"/>
-      <c r="E8" s="91"/>
-      <c r="F8" s="97" t="s">
+      <c r="H7" s="84"/>
+      <c r="I7" s="83"/>
+    </row>
+    <row r="8" s="59" customFormat="1" ht="17.25" customHeight="1" spans="1:9">
+      <c r="A8" s="79"/>
+      <c r="B8" s="75"/>
+      <c r="C8" s="75"/>
+      <c r="D8" s="80"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="101"/>
-      <c r="H8" s="101"/>
-      <c r="I8" s="99"/>
-    </row>
-    <row r="9" s="75" customFormat="1" ht="17.25" customHeight="1" spans="1:9">
-      <c r="A9" s="95"/>
-      <c r="B9" s="91"/>
-      <c r="C9" s="91"/>
-      <c r="D9" s="96"/>
-      <c r="E9" s="91"/>
-      <c r="F9" s="102" t="s">
+      <c r="G8" s="85"/>
+      <c r="H8" s="85"/>
+      <c r="I8" s="83"/>
+    </row>
+    <row r="9" s="59" customFormat="1" ht="17.25" customHeight="1" spans="1:9">
+      <c r="A9" s="79"/>
+      <c r="B9" s="75"/>
+      <c r="C9" s="75"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="86" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="98" t="s">
+      <c r="G9" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="98"/>
-      <c r="I9" s="99"/>
-    </row>
-    <row r="10" s="75" customFormat="1" ht="17.25" customHeight="1" spans="1:9">
-      <c r="A10" s="95"/>
-      <c r="B10" s="91"/>
-      <c r="C10" s="91"/>
-      <c r="D10" s="96"/>
-      <c r="E10" s="91"/>
-      <c r="F10" s="102" t="s">
+      <c r="H9" s="82"/>
+      <c r="I9" s="83"/>
+    </row>
+    <row r="10" s="59" customFormat="1" ht="17.25" customHeight="1" spans="1:9">
+      <c r="A10" s="79"/>
+      <c r="B10" s="75"/>
+      <c r="C10" s="75"/>
+      <c r="D10" s="80"/>
+      <c r="E10" s="75"/>
+      <c r="F10" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="98" t="s">
+      <c r="G10" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="103"/>
-      <c r="I10" s="99"/>
-    </row>
-    <row r="11" s="75" customFormat="1" ht="17.25" customHeight="1" spans="1:9">
-      <c r="A11" s="104"/>
-      <c r="B11" s="105"/>
-      <c r="C11" s="105"/>
-      <c r="D11" s="106"/>
-      <c r="E11" s="91"/>
-      <c r="F11" s="97" t="s">
+      <c r="H10" s="87"/>
+      <c r="I10" s="83"/>
+    </row>
+    <row r="11" s="59" customFormat="1" ht="17.25" customHeight="1" spans="1:9">
+      <c r="A11" s="88"/>
+      <c r="B11" s="89"/>
+      <c r="C11" s="89"/>
+      <c r="D11" s="90"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="107" t="e">
+      <c r="G11" s="91" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H11" s="107"/>
-      <c r="I11" s="99"/>
-    </row>
-    <row r="12" s="75" customFormat="1" ht="20.25" customHeight="1" spans="1:9">
-      <c r="A12" s="88" t="s">
+      <c r="H11" s="91"/>
+      <c r="I11" s="83"/>
+    </row>
+    <row r="12" s="59" customFormat="1" ht="20.25" customHeight="1" spans="1:9">
+      <c r="A12" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="89"/>
-      <c r="C12" s="89"/>
-      <c r="D12" s="90"/>
-      <c r="E12" s="91"/>
-      <c r="F12" s="97" t="s">
+      <c r="B12" s="73"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="75"/>
+      <c r="F12" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="G12" s="91" t="s">
+      <c r="G12" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="H12" s="91"/>
-      <c r="I12" s="96"/>
-    </row>
-    <row r="13" s="75" customFormat="1" ht="15.75" customHeight="1" spans="1:9">
-      <c r="A13" s="95" t="s">
+      <c r="H12" s="75"/>
+      <c r="I12" s="80"/>
+    </row>
+    <row r="13" s="59" customFormat="1" ht="15.75" customHeight="1" spans="1:9">
+      <c r="A13" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="91"/>
-      <c r="C13" s="91"/>
-      <c r="D13" s="96"/>
-      <c r="E13" s="91"/>
-      <c r="F13" s="108"/>
-      <c r="G13" s="91"/>
-      <c r="H13" s="91"/>
-      <c r="I13" s="96"/>
-    </row>
-    <row r="14" s="75" customFormat="1" ht="27" customHeight="1" spans="1:9">
-      <c r="A14" s="104"/>
-      <c r="B14" s="105"/>
-      <c r="C14" s="105"/>
-      <c r="D14" s="106"/>
-      <c r="E14" s="91"/>
-      <c r="F14" s="109"/>
-      <c r="G14" s="105" t="s">
+      <c r="B13" s="75"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="80"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="92"/>
+      <c r="G13" s="75"/>
+      <c r="H13" s="75"/>
+      <c r="I13" s="80"/>
+    </row>
+    <row r="14" s="59" customFormat="1" ht="27" customHeight="1" spans="1:9">
+      <c r="A14" s="88"/>
+      <c r="B14" s="89"/>
+      <c r="C14" s="89"/>
+      <c r="D14" s="90"/>
+      <c r="E14" s="75"/>
+      <c r="F14" s="93"/>
+      <c r="G14" s="89" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="105"/>
-      <c r="I14" s="106"/>
-    </row>
-    <row r="15" s="76" customFormat="1" ht="25" customHeight="1" spans="1:9">
-      <c r="A15" s="110" t="s">
+      <c r="H14" s="89"/>
+      <c r="I14" s="90"/>
+    </row>
+    <row r="15" s="60" customFormat="1" ht="25" customHeight="1" spans="1:9">
+      <c r="A15" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="111" t="s">
+      <c r="B15" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="111" t="s">
+      <c r="C15" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="111" t="s">
+      <c r="D15" s="94" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="111" t="s">
+      <c r="E15" s="94" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="111" t="s">
+      <c r="F15" s="94" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="112" t="s">
+      <c r="G15" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="H15" s="112" t="s">
+      <c r="H15" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="I15" s="113" t="s">
+      <c r="I15" s="95" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="16" s="76" customFormat="1" ht="25" customHeight="1" spans="1:9">
-      <c r="A16" s="114"/>
-      <c r="B16" s="111"/>
-      <c r="C16" s="111"/>
-      <c r="D16" s="111"/>
-      <c r="E16" s="114"/>
-      <c r="F16" s="111"/>
-      <c r="G16" s="115"/>
-      <c r="H16" s="112"/>
-      <c r="I16" s="115"/>
-    </row>
-    <row r="17" s="77" customFormat="1" ht="34" customHeight="1" spans="1:9">
-      <c r="A17" s="116"/>
-      <c r="B17" s="117" t="s">
+    <row r="16" s="60" customFormat="1" ht="25" customHeight="1" spans="1:9">
+      <c r="A16" s="96"/>
+      <c r="B16" s="94"/>
+      <c r="C16" s="94"/>
+      <c r="D16" s="94"/>
+      <c r="E16" s="96"/>
+      <c r="F16" s="94"/>
+      <c r="G16" s="97"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="97"/>
+    </row>
+    <row r="17" s="61" customFormat="1" ht="34" customHeight="1" spans="1:9">
+      <c r="A17" s="98"/>
+      <c r="B17" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="117"/>
-      <c r="D17" s="117"/>
-      <c r="E17" s="116"/>
-      <c r="F17" s="117"/>
-      <c r="G17" s="118"/>
-      <c r="H17" s="117"/>
-      <c r="I17" s="116"/>
-    </row>
-    <row r="18" s="77" customFormat="1" ht="34" customHeight="1" spans="1:9">
-      <c r="A18" s="116"/>
-      <c r="B18" s="119" t="s">
+      <c r="C17" s="99"/>
+      <c r="D17" s="99"/>
+      <c r="E17" s="98"/>
+      <c r="F17" s="99"/>
+      <c r="G17" s="100"/>
+      <c r="H17" s="99"/>
+      <c r="I17" s="98"/>
+    </row>
+    <row r="18" s="61" customFormat="1" ht="34" customHeight="1" spans="1:9">
+      <c r="A18" s="98"/>
+      <c r="B18" s="101" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="119"/>
-      <c r="D18" s="119"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="120"/>
-      <c r="G18" s="121"/>
-      <c r="H18" s="120" t="s">
+      <c r="C18" s="101"/>
+      <c r="D18" s="101"/>
+      <c r="E18" s="98"/>
+      <c r="F18" s="102"/>
+      <c r="G18" s="103"/>
+      <c r="H18" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="I18" s="116"/>
-    </row>
-    <row r="19" s="77" customFormat="1" ht="34" customHeight="1" spans="1:9">
-      <c r="A19" s="116"/>
-      <c r="B19" s="79"/>
-      <c r="C19" s="79"/>
-      <c r="D19" s="79"/>
-      <c r="E19" s="79"/>
-      <c r="F19" s="79"/>
-      <c r="G19" s="122"/>
-      <c r="H19" s="123"/>
-      <c r="I19" s="123"/>
-    </row>
-    <row r="20" s="77" customFormat="1" ht="34" customHeight="1" spans="1:9">
-      <c r="A20" s="124"/>
-      <c r="B20" s="125" t="s">
+      <c r="I18" s="98"/>
+    </row>
+    <row r="19" s="61" customFormat="1" ht="34" customHeight="1" spans="1:9">
+      <c r="A19" s="98"/>
+      <c r="B19" s="104"/>
+      <c r="C19" s="104"/>
+      <c r="D19" s="104"/>
+      <c r="E19" s="104"/>
+      <c r="F19" s="104"/>
+      <c r="G19" s="105"/>
+      <c r="H19" s="106"/>
+      <c r="I19" s="106"/>
+    </row>
+    <row r="20" s="61" customFormat="1" ht="34" customHeight="1" spans="1:9">
+      <c r="A20" s="107"/>
+      <c r="B20" s="108" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="125"/>
-      <c r="D20" s="125"/>
-      <c r="E20" s="125"/>
-      <c r="F20" s="126"/>
-      <c r="G20" s="124"/>
-      <c r="H20" s="127" t="s">
+      <c r="C20" s="108"/>
+      <c r="D20" s="108"/>
+      <c r="E20" s="108"/>
+      <c r="F20" s="109"/>
+      <c r="G20" s="107"/>
+      <c r="H20" s="110" t="s">
         <v>32</v>
       </c>
-      <c r="I20" s="127"/>
-    </row>
-    <row r="21" s="77" customFormat="1" ht="34" customHeight="1" spans="1:9">
-      <c r="A21" s="80"/>
-      <c r="B21" s="81"/>
-      <c r="C21" s="81"/>
-      <c r="D21" s="81"/>
-      <c r="E21" s="82"/>
-      <c r="H21" s="128"/>
-    </row>
-    <row r="22" s="77" customFormat="1" ht="34" customHeight="1" spans="1:9">
-      <c r="A22" s="80"/>
-      <c r="B22" s="81"/>
-      <c r="C22" s="81"/>
-      <c r="D22" s="81"/>
-      <c r="E22" s="82"/>
-      <c r="H22" s="128"/>
-    </row>
-    <row r="23" s="77" customFormat="1" ht="34" customHeight="1" spans="1:9">
-      <c r="A23" s="80"/>
-      <c r="B23" s="81"/>
-      <c r="C23" s="81"/>
-      <c r="D23" s="81"/>
-      <c r="E23" s="82"/>
-      <c r="F23" s="129"/>
-      <c r="H23" s="128"/>
-    </row>
-    <row r="24" s="77" customFormat="1" ht="34" customHeight="1" spans="1:9">
-      <c r="A24" s="80"/>
-      <c r="B24" s="81"/>
-      <c r="C24" s="81"/>
-      <c r="D24" s="81"/>
-      <c r="E24" s="82"/>
-      <c r="F24" s="129"/>
-      <c r="H24" s="128"/>
-    </row>
-    <row r="25" s="77" customFormat="1" ht="34" customHeight="1" spans="1:9">
-      <c r="A25" s="80"/>
-      <c r="B25" s="81"/>
-      <c r="C25" s="81"/>
-      <c r="D25" s="81"/>
-      <c r="E25" s="82"/>
-      <c r="H25" s="128"/>
-    </row>
-    <row r="26" s="77" customFormat="1" ht="34" customHeight="1" spans="1:9">
-      <c r="A26" s="80"/>
-      <c r="B26" s="81"/>
-      <c r="C26" s="81"/>
-      <c r="D26" s="81"/>
-      <c r="E26" s="82"/>
-      <c r="H26" s="128"/>
-    </row>
-    <row r="27" s="77" customFormat="1" ht="34" customHeight="1" spans="1:9">
-      <c r="A27" s="80"/>
-      <c r="B27" s="81"/>
-      <c r="C27" s="81"/>
-      <c r="D27" s="81"/>
-      <c r="E27" s="82"/>
-      <c r="F27" s="129"/>
-      <c r="H27" s="128"/>
-    </row>
-    <row r="28" s="78" customFormat="1" ht="24.75" customHeight="1" spans="1:9">
-      <c r="A28" s="80"/>
-      <c r="B28" s="81"/>
-      <c r="C28" s="81"/>
-      <c r="D28" s="81"/>
-      <c r="E28" s="82"/>
+      <c r="I20" s="110"/>
+    </row>
+    <row r="21" s="61" customFormat="1" ht="34" customHeight="1" spans="1:9">
+      <c r="A21" s="111"/>
+      <c r="B21" s="112"/>
+      <c r="C21" s="112"/>
+      <c r="D21" s="112"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="114"/>
+      <c r="G21" s="114"/>
+      <c r="H21" s="115"/>
+      <c r="I21" s="114"/>
+    </row>
+    <row r="22" s="61" customFormat="1" ht="34" customHeight="1" spans="1:9">
+      <c r="A22" s="64"/>
+      <c r="B22" s="65"/>
+      <c r="C22" s="65"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="66"/>
+      <c r="H22" s="116"/>
+    </row>
+    <row r="23" s="61" customFormat="1" ht="34" customHeight="1" spans="1:9">
+      <c r="A23" s="64"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="66"/>
+      <c r="F23" s="117"/>
+      <c r="H23" s="116"/>
+    </row>
+    <row r="24" s="61" customFormat="1" ht="34" customHeight="1" spans="1:9">
+      <c r="A24" s="64"/>
+      <c r="B24" s="65"/>
+      <c r="C24" s="65"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="66"/>
+      <c r="F24" s="117"/>
+      <c r="H24" s="116"/>
+    </row>
+    <row r="25" s="61" customFormat="1" ht="34" customHeight="1" spans="1:9">
+      <c r="A25" s="64"/>
+      <c r="B25" s="65"/>
+      <c r="C25" s="65"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="66"/>
+      <c r="H25" s="116"/>
+    </row>
+    <row r="26" s="61" customFormat="1" ht="34" customHeight="1" spans="1:9">
+      <c r="A26" s="64"/>
+      <c r="B26" s="65"/>
+      <c r="C26" s="65"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="66"/>
+      <c r="H26" s="116"/>
+    </row>
+    <row r="27" s="61" customFormat="1" ht="34" customHeight="1" spans="1:9">
+      <c r="A27" s="64"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="65"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="66"/>
+      <c r="F27" s="117"/>
+      <c r="H27" s="116"/>
+    </row>
+    <row r="28" s="62" customFormat="1" ht="24.75" customHeight="1" spans="1:9">
+      <c r="A28" s="64"/>
+      <c r="B28" s="65"/>
+      <c r="C28" s="65"/>
+      <c r="D28" s="65"/>
+      <c r="E28" s="66"/>
     </row>
     <row r="29" ht="30.4" customHeight="1" spans="1:9">
-      <c r="B29" s="81"/>
-      <c r="C29" s="81"/>
-      <c r="D29" s="81"/>
-      <c r="E29" s="82"/>
-      <c r="G29" s="80"/>
-      <c r="H29" s="80"/>
-      <c r="I29" s="80"/>
-    </row>
-    <row r="30" s="79" customFormat="1" ht="18" customHeight="1" spans="1:9">
-      <c r="A30" s="80"/>
-      <c r="B30" s="81"/>
-      <c r="C30" s="81"/>
-      <c r="D30" s="81"/>
-      <c r="E30" s="82"/>
+      <c r="B29" s="65"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="66"/>
+      <c r="G29" s="64"/>
+      <c r="H29" s="64"/>
+      <c r="I29" s="64"/>
+    </row>
+    <row r="30" s="63" customFormat="1" ht="18" customHeight="1" spans="1:9">
+      <c r="A30" s="64"/>
+      <c r="B30" s="65"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="66"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="B31" s="81"/>
-      <c r="C31" s="81"/>
-      <c r="D31" s="81"/>
-      <c r="E31" s="82"/>
-      <c r="G31" s="80"/>
-      <c r="H31" s="80"/>
-      <c r="I31" s="80"/>
+      <c r="B31" s="65"/>
+      <c r="C31" s="65"/>
+      <c r="D31" s="65"/>
+      <c r="E31" s="66"/>
+      <c r="G31" s="64"/>
+      <c r="H31" s="64"/>
+      <c r="I31" s="64"/>
     </row>
     <row r="32" spans="1:9">
-      <c r="B32" s="81"/>
-      <c r="C32" s="81"/>
-      <c r="D32" s="81"/>
-      <c r="E32" s="82"/>
-      <c r="G32" s="80"/>
-      <c r="H32" s="80"/>
-      <c r="I32" s="80"/>
+      <c r="B32" s="65"/>
+      <c r="C32" s="65"/>
+      <c r="D32" s="65"/>
+      <c r="E32" s="66"/>
+      <c r="G32" s="64"/>
+      <c r="H32" s="64"/>
+      <c r="I32" s="64"/>
     </row>
     <row r="33" spans="2:9">
-      <c r="B33" s="81"/>
-      <c r="C33" s="81"/>
-      <c r="D33" s="81"/>
-      <c r="E33" s="82"/>
-      <c r="G33" s="80"/>
-      <c r="H33" s="80"/>
-      <c r="I33" s="80"/>
+      <c r="B33" s="65"/>
+      <c r="C33" s="65"/>
+      <c r="D33" s="65"/>
+      <c r="E33" s="66"/>
+      <c r="G33" s="64"/>
+      <c r="H33" s="64"/>
+      <c r="I33" s="64"/>
     </row>
     <row r="34" spans="2:9">
-      <c r="B34" s="81"/>
-      <c r="C34" s="81"/>
-      <c r="D34" s="81"/>
-      <c r="E34" s="82"/>
-      <c r="G34" s="80"/>
-      <c r="H34" s="80"/>
-      <c r="I34" s="80"/>
+      <c r="B34" s="65"/>
+      <c r="C34" s="65"/>
+      <c r="D34" s="65"/>
+      <c r="E34" s="66"/>
+      <c r="G34" s="64"/>
+      <c r="H34" s="64"/>
+      <c r="I34" s="64"/>
     </row>
     <row r="35" spans="2:9">
-      <c r="B35" s="81"/>
-      <c r="C35" s="81"/>
-      <c r="D35" s="81"/>
-      <c r="E35" s="82"/>
-      <c r="G35" s="80"/>
-      <c r="H35" s="80"/>
-      <c r="I35" s="80"/>
+      <c r="B35" s="65"/>
+      <c r="C35" s="65"/>
+      <c r="D35" s="65"/>
+      <c r="E35" s="66"/>
+      <c r="G35" s="64"/>
+      <c r="H35" s="64"/>
+      <c r="I35" s="64"/>
     </row>
     <row r="36" spans="2:9">
-      <c r="B36" s="81"/>
-      <c r="C36" s="81"/>
-      <c r="D36" s="81"/>
-      <c r="E36" s="82"/>
-      <c r="G36" s="80"/>
-      <c r="H36" s="80"/>
-      <c r="I36" s="80"/>
+      <c r="B36" s="65"/>
+      <c r="C36" s="65"/>
+      <c r="D36" s="65"/>
+      <c r="E36" s="66"/>
+      <c r="G36" s="64"/>
+      <c r="H36" s="64"/>
+      <c r="I36" s="64"/>
     </row>
     <row r="37" spans="2:9">
-      <c r="B37" s="81"/>
-      <c r="C37" s="81"/>
-      <c r="D37" s="81"/>
-      <c r="E37" s="82"/>
-      <c r="G37" s="80"/>
-      <c r="H37" s="80"/>
-      <c r="I37" s="80"/>
+      <c r="B37" s="65"/>
+      <c r="C37" s="65"/>
+      <c r="D37" s="65"/>
+      <c r="E37" s="66"/>
+      <c r="G37" s="64"/>
+      <c r="H37" s="64"/>
+      <c r="I37" s="64"/>
     </row>
     <row r="38" spans="2:9">
-      <c r="B38" s="81"/>
-      <c r="C38" s="81"/>
-      <c r="D38" s="81"/>
-      <c r="E38" s="82"/>
-      <c r="G38" s="80"/>
-      <c r="H38" s="80"/>
-      <c r="I38" s="80"/>
+      <c r="B38" s="65"/>
+      <c r="C38" s="65"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="66"/>
+      <c r="G38" s="64"/>
+      <c r="H38" s="64"/>
+      <c r="I38" s="64"/>
     </row>
     <row r="39" spans="2:9">
-      <c r="B39" s="81"/>
-      <c r="C39" s="81"/>
-      <c r="D39" s="81"/>
-      <c r="E39" s="82"/>
-      <c r="G39" s="80"/>
-      <c r="H39" s="80"/>
-      <c r="I39" s="80"/>
+      <c r="B39" s="65"/>
+      <c r="C39" s="65"/>
+      <c r="D39" s="65"/>
+      <c r="E39" s="66"/>
+      <c r="G39" s="64"/>
+      <c r="H39" s="64"/>
+      <c r="I39" s="64"/>
     </row>
     <row r="40" spans="2:9">
-      <c r="B40" s="81"/>
-      <c r="C40" s="81"/>
-      <c r="D40" s="81"/>
-      <c r="E40" s="82"/>
-      <c r="G40" s="80"/>
-      <c r="H40" s="80"/>
-      <c r="I40" s="80"/>
+      <c r="B40" s="65"/>
+      <c r="C40" s="65"/>
+      <c r="D40" s="65"/>
+      <c r="E40" s="66"/>
+      <c r="G40" s="64"/>
+      <c r="H40" s="64"/>
+      <c r="I40" s="64"/>
     </row>
     <row r="41" spans="2:9">
-      <c r="B41" s="81"/>
-      <c r="C41" s="81"/>
-      <c r="D41" s="81"/>
-      <c r="E41" s="82"/>
-      <c r="G41" s="80"/>
-      <c r="H41" s="80"/>
-      <c r="I41" s="80"/>
+      <c r="B41" s="65"/>
+      <c r="C41" s="65"/>
+      <c r="D41" s="65"/>
+      <c r="E41" s="66"/>
+      <c r="G41" s="64"/>
+      <c r="H41" s="64"/>
+      <c r="I41" s="64"/>
     </row>
     <row r="42" spans="2:9">
-      <c r="B42" s="81"/>
-      <c r="C42" s="81"/>
-      <c r="D42" s="81"/>
-      <c r="E42" s="82"/>
-      <c r="G42" s="80"/>
-      <c r="H42" s="80"/>
-      <c r="I42" s="80"/>
+      <c r="B42" s="65"/>
+      <c r="C42" s="65"/>
+      <c r="D42" s="65"/>
+      <c r="E42" s="66"/>
+      <c r="G42" s="64"/>
+      <c r="H42" s="64"/>
+      <c r="I42" s="64"/>
     </row>
     <row r="43" spans="2:9">
-      <c r="B43" s="81"/>
-      <c r="C43" s="81"/>
-      <c r="D43" s="81"/>
-      <c r="E43" s="82"/>
-      <c r="G43" s="80"/>
-      <c r="H43" s="80"/>
-      <c r="I43" s="80"/>
+      <c r="B43" s="65"/>
+      <c r="C43" s="65"/>
+      <c r="D43" s="65"/>
+      <c r="E43" s="66"/>
+      <c r="G43" s="64"/>
+      <c r="H43" s="64"/>
+      <c r="I43" s="64"/>
     </row>
     <row r="44" spans="2:9">
-      <c r="B44" s="81"/>
-      <c r="C44" s="81"/>
-      <c r="D44" s="81"/>
-      <c r="E44" s="82"/>
-      <c r="G44" s="80"/>
-      <c r="H44" s="80"/>
-      <c r="I44" s="80"/>
+      <c r="B44" s="65"/>
+      <c r="C44" s="65"/>
+      <c r="D44" s="65"/>
+      <c r="E44" s="66"/>
+      <c r="G44" s="64"/>
+      <c r="H44" s="64"/>
+      <c r="I44" s="64"/>
     </row>
     <row r="45" spans="2:9">
-      <c r="B45" s="81"/>
-      <c r="C45" s="81"/>
-      <c r="D45" s="81"/>
-      <c r="E45" s="82"/>
-      <c r="G45" s="80"/>
-      <c r="H45" s="80"/>
-      <c r="I45" s="80"/>
+      <c r="B45" s="65"/>
+      <c r="C45" s="65"/>
+      <c r="D45" s="65"/>
+      <c r="E45" s="66"/>
+      <c r="G45" s="64"/>
+      <c r="H45" s="64"/>
+      <c r="I45" s="64"/>
     </row>
     <row r="46" spans="2:9">
-      <c r="B46" s="81"/>
-      <c r="C46" s="81"/>
-      <c r="D46" s="81"/>
-      <c r="E46" s="82"/>
-      <c r="G46" s="80"/>
-      <c r="H46" s="80"/>
-      <c r="I46" s="80"/>
+      <c r="B46" s="65"/>
+      <c r="C46" s="65"/>
+      <c r="D46" s="65"/>
+      <c r="E46" s="66"/>
+      <c r="G46" s="64"/>
+      <c r="H46" s="64"/>
+      <c r="I46" s="64"/>
     </row>
     <row r="47" spans="2:9">
-      <c r="B47" s="81"/>
-      <c r="C47" s="81"/>
-      <c r="D47" s="81"/>
-      <c r="E47" s="82"/>
-      <c r="G47" s="80"/>
-      <c r="H47" s="80"/>
-      <c r="I47" s="80"/>
+      <c r="B47" s="65"/>
+      <c r="C47" s="65"/>
+      <c r="D47" s="65"/>
+      <c r="E47" s="66"/>
+      <c r="G47" s="64"/>
+      <c r="H47" s="64"/>
+      <c r="I47" s="64"/>
     </row>
     <row r="48" spans="2:9">
-      <c r="B48" s="81"/>
-      <c r="C48" s="81"/>
-      <c r="D48" s="81"/>
-      <c r="E48" s="82"/>
-      <c r="G48" s="80"/>
-      <c r="H48" s="80"/>
-      <c r="I48" s="80"/>
+      <c r="B48" s="65"/>
+      <c r="C48" s="65"/>
+      <c r="D48" s="65"/>
+      <c r="E48" s="66"/>
+      <c r="G48" s="64"/>
+      <c r="H48" s="64"/>
+      <c r="I48" s="64"/>
     </row>
     <row r="49" spans="2:9">
-      <c r="B49" s="81"/>
-      <c r="C49" s="81"/>
-      <c r="D49" s="81"/>
-      <c r="E49" s="82"/>
-      <c r="G49" s="80"/>
-      <c r="H49" s="80"/>
-      <c r="I49" s="80"/>
+      <c r="B49" s="65"/>
+      <c r="C49" s="65"/>
+      <c r="D49" s="65"/>
+      <c r="E49" s="66"/>
+      <c r="G49" s="64"/>
+      <c r="H49" s="64"/>
+      <c r="I49" s="64"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" formatCells="0"/>
@@ -3283,157 +3252,157 @@
   <dimension ref="A1:H10"/>
   <sheetFormatPr defaultColWidth="8" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="6.08333333333333" style="49" customWidth="1"/>
-    <col min="2" max="3" width="25.3333333333333" style="49" customWidth="1"/>
-    <col min="4" max="4" width="11.0833333333333" style="49" customWidth="1"/>
-    <col min="5" max="5" width="9.08333333333333" style="49" customWidth="1"/>
-    <col min="6" max="6" width="7.25" style="49" customWidth="1"/>
-    <col min="7" max="7" width="10.0833333333333" style="49" customWidth="1"/>
-    <col min="8" max="8" width="13.25" style="49" customWidth="1"/>
-    <col min="9" max="16364" width="8" style="50"/>
+    <col min="1" max="1" width="6.08333333333333" style="33" customWidth="1"/>
+    <col min="2" max="3" width="25.3333333333333" style="33" customWidth="1"/>
+    <col min="4" max="4" width="11.0833333333333" style="33" customWidth="1"/>
+    <col min="5" max="5" width="9.08333333333333" style="33" customWidth="1"/>
+    <col min="6" max="6" width="7.25" style="33" customWidth="1"/>
+    <col min="7" max="7" width="10.0833333333333" style="33" customWidth="1"/>
+    <col min="8" max="8" width="13.25" style="33" customWidth="1"/>
+    <col min="9" max="16364" width="8" style="34"/>
   </cols>
   <sheetData>
     <row r="1" ht="35.15" customHeight="1" spans="1:8">
-      <c r="A1" s="51" t="str">
+      <c r="A1" s="35" t="str">
         <f>合同!A1</f>
         <v>成都玖马赫供应链管理有限公司</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
     </row>
     <row r="2" ht="26.15" customHeight="1" spans="1:8">
-      <c r="A2" s="67" t="str">
+      <c r="A2" s="51" t="str">
         <f>合同!A2</f>
         <v>CHENGDU JUMACH SUPPLY CHAIN MANAGEMENT CO.,LTD</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:8">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
     </row>
     <row r="4" ht="20.4" spans="1:8">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-    </row>
-    <row r="5" s="48" customFormat="1" ht="21" spans="1:8">
-      <c r="A5" s="54" t="s">
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
+    </row>
+    <row r="5" s="32" customFormat="1" ht="21" spans="1:8">
+      <c r="A5" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-    </row>
-    <row r="6" s="48" customFormat="1" ht="21" spans="1:8">
-      <c r="A6" s="69" t="s">
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+    </row>
+    <row r="6" s="32" customFormat="1" ht="21" spans="1:8">
+      <c r="A6" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="69"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-    </row>
-    <row r="7" s="48" customFormat="1" ht="28" customHeight="1" spans="1:8">
-      <c r="A7" s="71" t="s">
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+    </row>
+    <row r="7" s="32" customFormat="1" ht="28" customHeight="1" spans="1:8">
+      <c r="A7" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="71"/>
-      <c r="C7" s="71"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="59" t="s">
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="70" t="s">
+      <c r="G7" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="70"/>
-    </row>
-    <row r="8" s="48" customFormat="1" ht="24" customHeight="1" spans="1:8">
-      <c r="A8" s="71"/>
-      <c r="B8" s="71"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="57" t="s">
+      <c r="H7" s="54"/>
+    </row>
+    <row r="8" s="32" customFormat="1" ht="24" customHeight="1" spans="1:8">
+      <c r="A8" s="55"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="60"/>
-    </row>
-    <row r="9" s="48" customFormat="1" ht="21" spans="1:8">
-      <c r="A9" s="72" t="s">
+      <c r="G8" s="44"/>
+    </row>
+    <row r="9" s="32" customFormat="1" ht="21" spans="1:8">
+      <c r="A9" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="59" t="s">
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="61">
+      <c r="G9" s="45">
         <f>合同!G6</f>
         <v>46167</v>
       </c>
-      <c r="H9" s="61"/>
-    </row>
-    <row r="10" s="49" customFormat="1" ht="34" customHeight="1" spans="1:8">
-      <c r="A10" s="62" t="s">
+      <c r="H9" s="45"/>
+    </row>
+    <row r="10" s="33" customFormat="1" ht="34" customHeight="1" spans="1:8">
+      <c r="A10" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="63" t="s">
+      <c r="B10" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="63" t="s">
+      <c r="C10" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="63" t="s">
+      <c r="D10" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="63" t="s">
+      <c r="E10" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="63" t="s">
+      <c r="F10" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="63" t="s">
+      <c r="G10" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="63" t="s">
+      <c r="H10" s="47" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3463,206 +3432,206 @@
   <dimension ref="A1:M21"/>
   <sheetFormatPr defaultColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="6.33333333333333" style="49" customWidth="1"/>
-    <col min="2" max="2" width="25.0833333333333" style="49" customWidth="1"/>
-    <col min="3" max="3" width="20.25" style="49" customWidth="1"/>
-    <col min="4" max="4" width="10.25" style="49" customWidth="1"/>
-    <col min="5" max="5" width="6.08333333333333" style="49" customWidth="1"/>
-    <col min="6" max="6" width="6" style="49" customWidth="1"/>
-    <col min="7" max="7" width="6.75" style="49" customWidth="1"/>
-    <col min="8" max="8" width="7.75" style="49" customWidth="1"/>
-    <col min="9" max="9" width="6.08333333333333" style="49" customWidth="1"/>
-    <col min="10" max="12" width="3.75" style="49" customWidth="1"/>
-    <col min="13" max="13" width="8.33333333333333" style="50"/>
-    <col min="14" max="16384" width="8" style="50"/>
+    <col min="1" max="1" width="6.33333333333333" style="33" customWidth="1"/>
+    <col min="2" max="2" width="25.0833333333333" style="33" customWidth="1"/>
+    <col min="3" max="3" width="20.25" style="33" customWidth="1"/>
+    <col min="4" max="4" width="10.25" style="33" customWidth="1"/>
+    <col min="5" max="5" width="6.08333333333333" style="33" customWidth="1"/>
+    <col min="6" max="6" width="6" style="33" customWidth="1"/>
+    <col min="7" max="7" width="6.75" style="33" customWidth="1"/>
+    <col min="8" max="8" width="7.75" style="33" customWidth="1"/>
+    <col min="9" max="9" width="6.08333333333333" style="33" customWidth="1"/>
+    <col min="10" max="12" width="3.75" style="33" customWidth="1"/>
+    <col min="13" max="13" width="8.33333333333333" style="34"/>
+    <col min="14" max="16384" width="8" style="34"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:13">
-      <c r="A1" s="51" t="str">
+      <c r="A1" s="35" t="str">
         <f>合同!A1</f>
         <v>成都玖马赫供应链管理有限公司</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" ht="27" customHeight="1" spans="1:13">
-      <c r="A2" s="51" t="str">
+      <c r="A2" s="35" t="str">
         <f>合同!A2</f>
         <v>CHENGDU JUMACH SUPPLY CHAIN MANAGEMENT CO.,LTD</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:13">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="36"/>
     </row>
     <row r="4" ht="20.4" spans="1:13">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="53"/>
-    </row>
-    <row r="5" s="48" customFormat="1" ht="21" spans="1:13">
-      <c r="A5" s="54" t="s">
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+    </row>
+    <row r="5" s="32" customFormat="1" ht="21" spans="1:13">
+      <c r="A5" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-    </row>
-    <row r="6" s="48" customFormat="1" ht="21" spans="1:13">
-      <c r="A6" s="55" t="str">
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
+      <c r="J5" s="38"/>
+      <c r="K5" s="38"/>
+      <c r="L5" s="38"/>
+    </row>
+    <row r="6" s="32" customFormat="1" ht="21" spans="1:13">
+      <c r="A6" s="39" t="str">
         <f>INVOICE!A6</f>
         <v>TO：Hong Kong Cammy Yeson Limited</v>
       </c>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-      <c r="L6" s="54"/>
-    </row>
-    <row r="7" s="48" customFormat="1" ht="30" customHeight="1" spans="1:13">
-      <c r="A7" s="58" t="str">
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="L6" s="38"/>
+    </row>
+    <row r="7" s="32" customFormat="1" ht="30" customHeight="1" spans="1:13">
+      <c r="A7" s="42" t="str">
         <f>INVOICE!A7</f>
         <v>C/O 1175 Florence Columbus Road UNITB（A12-A35）Bordentown New Jersey 08505</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="59" t="s">
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="60" t="str">
+      <c r="H7" s="44" t="str">
         <f>INVOICE!G7</f>
         <v>INV10645-260529-0004</v>
       </c>
-      <c r="I7" s="60"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="60"/>
-      <c r="L7" s="60"/>
-    </row>
-    <row r="8" s="48" customFormat="1" ht="30" customHeight="1" spans="1:13">
-      <c r="A8" s="58"/>
-      <c r="B8" s="58"/>
-      <c r="C8" s="58"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="59" t="s">
+      <c r="I7" s="44"/>
+      <c r="J7" s="44"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="44"/>
+    </row>
+    <row r="8" s="32" customFormat="1" ht="30" customHeight="1" spans="1:13">
+      <c r="A8" s="42"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="61">
+      <c r="H8" s="45">
         <f>INVOICE!G9</f>
         <v>46167</v>
       </c>
-      <c r="I8" s="61"/>
-      <c r="J8" s="61"/>
-      <c r="K8" s="61"/>
-      <c r="L8" s="61"/>
-    </row>
-    <row r="9" s="49" customFormat="1" ht="38.15" customHeight="1" spans="1:13">
-      <c r="A9" s="62" t="s">
+      <c r="I8" s="45"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="45"/>
+    </row>
+    <row r="9" s="33" customFormat="1" ht="38.15" customHeight="1" spans="1:13">
+      <c r="A9" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="62" t="s">
+      <c r="B9" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="62" t="s">
+      <c r="C9" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="62" t="s">
+      <c r="D9" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="63" t="s">
+      <c r="E9" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="64" t="s">
+      <c r="F9" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="62" t="s">
+      <c r="G9" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="H9" s="62" t="s">
+      <c r="H9" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="I9" s="65" t="s">
+      <c r="I9" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="65"/>
-      <c r="K9" s="65"/>
-      <c r="L9" s="65"/>
-    </row>
-    <row r="10" s="49" customFormat="1" ht="35.25" customHeight="1" spans="1:13">
-      <c r="M10" s="66"/>
-    </row>
-    <row r="11" s="49" customFormat="1" ht="35.25" customHeight="1"/>
-    <row r="12" s="49" customFormat="1" ht="35.25" customHeight="1"/>
-    <row r="13" s="49" customFormat="1" ht="35.25" customHeight="1"/>
-    <row r="14" s="49" customFormat="1" ht="35.25" customHeight="1"/>
-    <row r="15" s="49" customFormat="1" ht="35.25" customHeight="1"/>
-    <row r="16" s="49" customFormat="1" ht="35.25" customHeight="1"/>
-    <row r="17" s="49" customFormat="1" ht="35.25" customHeight="1"/>
-    <row r="18" s="49" customFormat="1" ht="25" customHeight="1"/>
-    <row r="19" s="49" customFormat="1" ht="27" customHeight="1"/>
-    <row r="20" s="49" customFormat="1" ht="34.5" customHeight="1"/>
-    <row r="21" s="49" customFormat="1" ht="27" customHeight="1"/>
+      <c r="J9" s="49"/>
+      <c r="K9" s="49"/>
+      <c r="L9" s="49"/>
+    </row>
+    <row r="10" s="33" customFormat="1" ht="35.25" customHeight="1" spans="1:13">
+      <c r="M10" s="50"/>
+    </row>
+    <row r="11" s="33" customFormat="1" ht="35.25" customHeight="1"/>
+    <row r="12" s="33" customFormat="1" ht="35.25" customHeight="1"/>
+    <row r="13" s="33" customFormat="1" ht="35.25" customHeight="1"/>
+    <row r="14" s="33" customFormat="1" ht="35.25" customHeight="1"/>
+    <row r="15" s="33" customFormat="1" ht="35.25" customHeight="1"/>
+    <row r="16" s="33" customFormat="1" ht="35.25" customHeight="1"/>
+    <row r="17" s="33" customFormat="1" ht="35.25" customHeight="1"/>
+    <row r="18" s="33" customFormat="1" ht="25" customHeight="1"/>
+    <row r="19" s="33" customFormat="1" ht="27" customHeight="1"/>
+    <row r="20" s="33" customFormat="1" ht="34.5" customHeight="1"/>
+    <row r="21" s="33" customFormat="1" ht="27" customHeight="1"/>
   </sheetData>
   <sheetProtection sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="9">
@@ -3935,104 +3904,116 @@
       <c r="A10" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="F10" s="25" t="s">
+      <c r="F10" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="G10" s="28" t="s">
+      <c r="G10" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="H10" s="29" t="s">
+      <c r="H10" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="I10" s="25" t="s">
+      <c r="I10" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25" t="s">
+      <c r="J10" s="24"/>
+      <c r="K10" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="L10" s="25"/>
-      <c r="M10" s="30" t="s">
+      <c r="L10" s="24"/>
+      <c r="M10" s="24" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" spans="1:13">
-      <c r="B11" s="25"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="34"/>
-      <c r="M11" s="35"/>
+    <row r="11" s="2" customFormat="1" ht="15.6" spans="1:13">
+      <c r="A11"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="27"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="24"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="11.4" spans="1:13">
-      <c r="A12" s="36" t="s">
+      <c r="A12" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="D12" s="29"/>
+      <c r="E12" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="F12" s="25"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="37" t="s">
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="39"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31"/>
+      <c r="M12" s="30"/>
     </row>
     <row r="13" s="1" customFormat="1" ht="10.8" spans="1:13">
-      <c r="A13" s="40"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="L13" s="38"/>
-      <c r="M13" s="39"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="31"/>
+      <c r="M13" s="30"/>
     </row>
     <row r="14" s="1" customFormat="1" ht="11.4" spans="1:13">
-      <c r="A14" s="42" t="s">
+      <c r="A14" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="22" t="s">
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="G14" s="23"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="47"/>
-    </row>
-    <row r="15" s="1" customFormat="1"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="10.8"/>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B1:L1"/>
